--- a/X-Series/XD12R/Jig/XD12R_GT1009A1R0_XC24R_GT1033A0R0/Docs/Firmware_Development_Documentation.xlsx
+++ b/X-Series/XD12R/Jig/XD12R_GT1009A1R0_XC24R_GT1033A0R0/Docs/Firmware_Development_Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD12R\Jig\XD12R_GT1009A1R0_XC24R_GT1033A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D9F41D-B225-40F4-855C-DD2D3B586840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C24AE6-FCBD-41C7-9F70-4D636F61A879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,12 @@
     <sheet name="Static Analysis" sheetId="6" r:id="rId6"/>
     <sheet name="Release Note" sheetId="7" r:id="rId7"/>
     <sheet name="Traceability" sheetId="8" r:id="rId8"/>
+    <sheet name="Common" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Architecture!$B$2:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Release Note'!$B$2:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Requirement!$B$2:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Requirement!$B$2:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Software Design'!$B$2:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Static Analysis'!$B$2:$M$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'System Test'!$B$2:$L$7</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="275">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -136,611 +137,819 @@
     <t>Related Requirement</t>
   </si>
   <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>ARC-002</t>
+  </si>
+  <si>
+    <t>ARC-003</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>XCR24 Driver</t>
+  </si>
+  <si>
+    <t>SPI Driver</t>
+  </si>
+  <si>
+    <t>ARC-004</t>
+  </si>
+  <si>
+    <t>Provide SPI communication.</t>
+  </si>
+  <si>
+    <t>ARC-005</t>
+  </si>
+  <si>
+    <t>Design ID</t>
+  </si>
+  <si>
+    <t>Function / Item</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
+  </si>
+  <si>
+    <t>DES-001</t>
+  </si>
+  <si>
+    <t>xcr24_init()</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>status_t</t>
+  </si>
+  <si>
+    <t>Initialize XCR24 registers and operating state.</t>
+  </si>
+  <si>
+    <t>Initialization error</t>
+  </si>
+  <si>
+    <t>DES-002</t>
+  </si>
+  <si>
+    <t>xcr24_write_reg()</t>
+  </si>
+  <si>
+    <t>Address, Data</t>
+  </si>
+  <si>
+    <t>Write XCR24 register through SPI.</t>
+  </si>
+  <si>
+    <t>SPI error/timeout</t>
+  </si>
+  <si>
+    <t>DES-003</t>
+  </si>
+  <si>
+    <t>xcr24_set_dac()</t>
+  </si>
+  <si>
+    <t>uint16_t dac_value</t>
+  </si>
+  <si>
+    <t>Set DAC value within 0~4095.</t>
+  </si>
+  <si>
+    <t>Invalid parameter</t>
+  </si>
+  <si>
+    <t>DES-004</t>
+  </si>
+  <si>
+    <t>xcr24_trim()</t>
+  </si>
+  <si>
+    <t>Trim parameter</t>
+  </si>
+  <si>
+    <t>trim_result_t</t>
+  </si>
+  <si>
+    <t>Perform DAC trim sequence.</t>
+  </si>
+  <si>
+    <t>ADC/trim failure</t>
+  </si>
+  <si>
+    <t>Test ID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Module / Function</t>
+  </si>
+  <si>
+    <t>Test Condition</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>PASS/FAIL</t>
+  </si>
+  <si>
+    <t>UT-001</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Minimum value</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>STATUS_OK</t>
+  </si>
+  <si>
+    <t>UT-002</t>
+  </si>
+  <si>
+    <t>Nominal value</t>
+  </si>
+  <si>
+    <t>2048</t>
+  </si>
+  <si>
+    <t>UT-003</t>
+  </si>
+  <si>
+    <t>Maximum value</t>
+  </si>
+  <si>
+    <t>4095</t>
+  </si>
+  <si>
+    <t>UT-004</t>
+  </si>
+  <si>
+    <t>Out of range</t>
+  </si>
+  <si>
+    <t>4096</t>
+  </si>
+  <si>
+    <t>STATUS_INVALID_PARAM</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>UART→Command→XCR24</t>
+  </si>
+  <si>
+    <t>Set DAC command</t>
+  </si>
+  <si>
+    <t>DAC=2048</t>
+  </si>
+  <si>
+    <t>XCR24 DAC register = 2048</t>
+  </si>
+  <si>
+    <t>FW-REQ-002,003</t>
+  </si>
+  <si>
+    <t>Test Item</t>
+  </si>
+  <si>
+    <t>Test Procedure</t>
+  </si>
+  <si>
+    <t>FW Version</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Power-on initialization</t>
+  </si>
+  <si>
+    <t>Power ON and monitor initialization sequence.</t>
+  </si>
+  <si>
+    <t>XCR24 initialization completes normally.</t>
+  </si>
+  <si>
+    <t>V1.0.0</t>
+  </si>
+  <si>
+    <t>ST-002</t>
+  </si>
+  <si>
+    <t>SPI register R/W</t>
+  </si>
+  <si>
+    <t>Read/write selected XCR24 registers.</t>
+  </si>
+  <si>
+    <t>Written data is read back correctly.</t>
+  </si>
+  <si>
+    <t>DAC output</t>
+  </si>
+  <si>
+    <t>Set DAC to 0/1024/2048/3072/4095 and measure output.</t>
+  </si>
+  <si>
+    <t>Output follows expected DAC setting.</t>
+  </si>
+  <si>
+    <t>ADC measurement</t>
+  </si>
+  <si>
+    <t>Measure known analog input values.</t>
+  </si>
+  <si>
+    <t>Measured values are within specification.</t>
+  </si>
+  <si>
+    <t>DAC trim</t>
+  </si>
+  <si>
+    <t>Run trim sequence and repeat measurement.</t>
+  </si>
+  <si>
+    <t>Trim completes and result is PASS within limits.</t>
+  </si>
+  <si>
+    <t>Finding ID</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Disposition</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>SA-001</t>
+  </si>
+  <si>
+    <t>IAR Static Analysis</t>
+  </si>
+  <si>
+    <t>MISRA-C:2012 Rule 14.4</t>
+  </si>
+  <si>
+    <t>xcr24.c</t>
+  </si>
+  <si>
+    <t>Controlling expression violation.</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>Modify condition</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>SA-002</t>
+  </si>
+  <si>
+    <t>cppcheck</t>
+  </si>
+  <si>
+    <t>MISRA-C:2012 Rule 10.8</t>
+  </si>
+  <si>
+    <t>trim.c</t>
+  </si>
+  <si>
+    <t>Cast expression issue.</t>
+  </si>
+  <si>
+    <t>Review cast</t>
+  </si>
+  <si>
+    <t>Deviation</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>XCR24</t>
+  </si>
+  <si>
+    <t>MCU</t>
+  </si>
+  <si>
+    <t>STM32F446RE</t>
+  </si>
+  <si>
+    <t>Compiler</t>
+  </si>
+  <si>
+    <t>IAR</t>
+  </si>
+  <si>
+    <t>Git Commit</t>
+  </si>
+  <si>
+    <t>Build Date</t>
+  </si>
+  <si>
+    <t>Release Date</t>
+  </si>
+  <si>
+    <t>Release Type</t>
+  </si>
+  <si>
+    <t>Initial Release</t>
+  </si>
+  <si>
+    <t>Added</t>
+  </si>
+  <si>
+    <t>Changed</t>
+  </si>
+  <si>
+    <t>Unit Test</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Static Analysis / MISRA</t>
+  </si>
+  <si>
+    <t>Binary</t>
+  </si>
+  <si>
+    <t>XCR24_FW_V1.0.0.hex / .bin</t>
+  </si>
+  <si>
+    <t>Architecture ID</t>
+  </si>
+  <si>
+    <t>Source File / Function</t>
+  </si>
+  <si>
+    <t>Unit/Integration Test ID</t>
+  </si>
+  <si>
+    <t>System Test ID</t>
+  </si>
+  <si>
+    <t>Static Analysis</t>
+  </si>
+  <si>
+    <t>Release Version</t>
+  </si>
+  <si>
+    <t>Overall Status</t>
+  </si>
+  <si>
+    <t>XCR24 initialization</t>
+  </si>
+  <si>
+    <t>ARC-001, ARC-003</t>
+  </si>
+  <si>
+    <t>xcr24.c / xcr24_init()</t>
+  </si>
+  <si>
+    <t>XCR24 SPI register R/W</t>
+  </si>
+  <si>
+    <t>ARC-003, ARC-004</t>
+  </si>
+  <si>
+    <t>drv_xcr24.c / xcr24_write_reg()</t>
+  </si>
+  <si>
+    <t>12-bit DAC setting</t>
+  </si>
+  <si>
+    <t>drv_xcr24.c / xcr24_set_dac()</t>
+  </si>
+  <si>
+    <t>UT-001~004</t>
+  </si>
+  <si>
+    <t>drv_adc.c / adc_measure()</t>
+  </si>
+  <si>
+    <t>xcr24_trim.c / xcr24_trim()</t>
+  </si>
+  <si>
+    <t>FW-REQ-001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trim</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FW-REQ-006</t>
+  </si>
+  <si>
+    <t>FW-REQ-007</t>
+  </si>
+  <si>
+    <t>FW-REQ-008</t>
+  </si>
+  <si>
+    <t>FW-REQ-009</t>
+  </si>
+  <si>
+    <t>FW-REQ-010</t>
+  </si>
+  <si>
+    <t>FW-REQ-011</t>
+  </si>
+  <si>
+    <t>FW-REQ-012</t>
+  </si>
+  <si>
+    <t>FW-REQ-013</t>
+  </si>
+  <si>
+    <t>FW-REQ-014</t>
+  </si>
+  <si>
+    <t>Measurement</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall measure the voltage of XC/XD output.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall measure the frequency of XC/XD output.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall generate configurable-frequency VSYNC signals for XC24R and XD12R.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall perform XC24R trim and return the result.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall perform XC24R test and provide the result.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall perform XD12R trim and return the result.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall perform XD12R test and provide the result.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interface</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall control XC24R through SPI.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall not issue a new command until the previous XD12R command has been completed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall control XD12R through the Serial Interface and via XC24R.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall provide a UART-based command line interface for PC communication.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall measure the current of XD output.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Implemented</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Integration Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>System Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Priority</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>High</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mid</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24R Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XD12R Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control XC24R registers and functions.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control XD12R registers and functions.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24R Driver / Timer Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Timer Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32 LL / TIM / DMA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UART Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FW-REQ-003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARC-006</t>
+  </si>
+  <si>
+    <t>ARC-007</t>
+  </si>
+  <si>
+    <t>ARC-008</t>
+  </si>
+  <si>
+    <t>ARC-009</t>
+  </si>
+  <si>
+    <t>Provide UART communication.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32 LL / UART / 115200bps</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAC7574 Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control DAC7574 registers and functions.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2C Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide I2C communication.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32 HAL / I2C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall control DAC7574 using I2C.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall control ADS114S08 using SPI.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADS114S08 Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPI Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24R Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24R Trim</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XD12R Trim</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XD12R Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Execute trim sequences.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Execute test sequences.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARC-010</t>
+  </si>
+  <si>
+    <t>ARC-011</t>
+  </si>
+  <si>
+    <t>ARC-012</t>
+  </si>
+  <si>
+    <t>ARC-015</t>
+  </si>
+  <si>
+    <t>FW-REQ-015</t>
+  </si>
+  <si>
+    <t>Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall perform LED Brightness control.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED Control</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Execute LED test sequences.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24R Driver / XD12R Driver / Timer Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32 LL / SPI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Command Line Interface</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parse received commands and dispatch corresponding application functions.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UART Driver / Application modules</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>System Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FW-REQ-016</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO Driver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Control GPIO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STM32 LL / GPIO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24R Driver / Timer Driver / GPIO Driver / Frequency Measure / Voltage Measure / Current Measure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XD12R Driver / Timer Driver / GPIO Driver  / Frequency Measure / Voltage Measure / Current Measure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XC24R Driver / Timer Driver / GPIO Driver  / Frequency Measure / Voltage Measure / Current Measure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FW-REQ-002, 006, 009, 010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide timer-based PWM, DMA, interrupt, and microsecond delay functions.
+Convert timer count value to frequency.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FW-REQ-005, 007, 008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARC-013</t>
+  </si>
+  <si>
+    <t>ARC-014</t>
+  </si>
+  <si>
+    <t>Control ADS114S08 registers and functions.
+Convert ADC raw value to voltage or current.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware shall control GPIO for trim and test.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>ARC-001</t>
-  </si>
-  <si>
-    <t>Application</t>
-  </si>
-  <si>
-    <t>XCR24 Test</t>
-  </si>
-  <si>
-    <t>Execute product/test sequences.</t>
-  </si>
-  <si>
-    <t>Framework</t>
-  </si>
-  <si>
-    <t>FW-REQ-001~005</t>
-  </si>
-  <si>
-    <t>ARC-002</t>
-  </si>
-  <si>
-    <t>Command Manager</t>
-  </si>
-  <si>
-    <t>ARC-003</t>
-  </si>
-  <si>
-    <t>Driver</t>
-  </si>
-  <si>
-    <t>XCR24 Driver</t>
-  </si>
-  <si>
-    <t>Control XCR24 registers and functions.</t>
-  </si>
-  <si>
-    <t>SPI Driver</t>
-  </si>
-  <si>
-    <t>FW-REQ-002~005</t>
-  </si>
-  <si>
-    <t>ARC-004</t>
-  </si>
-  <si>
-    <t>Provide SPI communication.</t>
-  </si>
-  <si>
-    <t>STM32 LL</t>
-  </si>
-  <si>
-    <t>ARC-005</t>
-  </si>
-  <si>
-    <t>ADC Driver</t>
-  </si>
-  <si>
-    <t>Acquire ADC measurements.</t>
-  </si>
-  <si>
-    <t>STM32 LL / ADC</t>
-  </si>
-  <si>
-    <t>Design ID</t>
-  </si>
-  <si>
-    <t>Function / Item</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Error Handling</t>
-  </si>
-  <si>
-    <t>DES-001</t>
-  </si>
-  <si>
-    <t>xcr24_init()</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>status_t</t>
-  </si>
-  <si>
-    <t>Initialize XCR24 registers and operating state.</t>
-  </si>
-  <si>
-    <t>Initialization error</t>
-  </si>
-  <si>
-    <t>DES-002</t>
-  </si>
-  <si>
-    <t>xcr24_write_reg()</t>
-  </si>
-  <si>
-    <t>Address, Data</t>
-  </si>
-  <si>
-    <t>Write XCR24 register through SPI.</t>
-  </si>
-  <si>
-    <t>SPI error/timeout</t>
-  </si>
-  <si>
-    <t>DES-003</t>
-  </si>
-  <si>
-    <t>xcr24_set_dac()</t>
-  </si>
-  <si>
-    <t>uint16_t dac_value</t>
-  </si>
-  <si>
-    <t>Set DAC value within 0~4095.</t>
-  </si>
-  <si>
-    <t>Invalid parameter</t>
-  </si>
-  <si>
-    <t>DES-004</t>
-  </si>
-  <si>
-    <t>xcr24_trim()</t>
-  </si>
-  <si>
-    <t>Trim parameter</t>
-  </si>
-  <si>
-    <t>trim_result_t</t>
-  </si>
-  <si>
-    <t>Perform DAC trim sequence.</t>
-  </si>
-  <si>
-    <t>ADC/trim failure</t>
-  </si>
-  <si>
-    <t>Test ID</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Module / Function</t>
-  </si>
-  <si>
-    <t>Test Condition</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>PASS/FAIL</t>
-  </si>
-  <si>
-    <t>UT-001</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Minimum value</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>STATUS_OK</t>
-  </si>
-  <si>
-    <t>UT-002</t>
-  </si>
-  <si>
-    <t>Nominal value</t>
-  </si>
-  <si>
-    <t>2048</t>
-  </si>
-  <si>
-    <t>UT-003</t>
-  </si>
-  <si>
-    <t>Maximum value</t>
-  </si>
-  <si>
-    <t>4095</t>
-  </si>
-  <si>
-    <t>UT-004</t>
-  </si>
-  <si>
-    <t>Out of range</t>
-  </si>
-  <si>
-    <t>4096</t>
-  </si>
-  <si>
-    <t>STATUS_INVALID_PARAM</t>
-  </si>
-  <si>
-    <t>Integration</t>
-  </si>
-  <si>
-    <t>UART→Command→XCR24</t>
-  </si>
-  <si>
-    <t>Set DAC command</t>
-  </si>
-  <si>
-    <t>DAC=2048</t>
-  </si>
-  <si>
-    <t>XCR24 DAC register = 2048</t>
-  </si>
-  <si>
-    <t>FW-REQ-002,003</t>
-  </si>
-  <si>
-    <t>Test Item</t>
-  </si>
-  <si>
-    <t>Test Procedure</t>
-  </si>
-  <si>
-    <t>FW Version</t>
-  </si>
-  <si>
-    <t>Tester</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Power-on initialization</t>
-  </si>
-  <si>
-    <t>Power ON and monitor initialization sequence.</t>
-  </si>
-  <si>
-    <t>XCR24 initialization completes normally.</t>
-  </si>
-  <si>
-    <t>V1.0.0</t>
-  </si>
-  <si>
-    <t>ST-002</t>
-  </si>
-  <si>
-    <t>SPI register R/W</t>
-  </si>
-  <si>
-    <t>Read/write selected XCR24 registers.</t>
-  </si>
-  <si>
-    <t>Written data is read back correctly.</t>
-  </si>
-  <si>
-    <t>DAC output</t>
-  </si>
-  <si>
-    <t>Set DAC to 0/1024/2048/3072/4095 and measure output.</t>
-  </si>
-  <si>
-    <t>Output follows expected DAC setting.</t>
-  </si>
-  <si>
-    <t>ADC measurement</t>
-  </si>
-  <si>
-    <t>Measure known analog input values.</t>
-  </si>
-  <si>
-    <t>Measured values are within specification.</t>
-  </si>
-  <si>
-    <t>DAC trim</t>
-  </si>
-  <si>
-    <t>Run trim sequence and repeat measurement.</t>
-  </si>
-  <si>
-    <t>Trim completes and result is PASS within limits.</t>
-  </si>
-  <si>
-    <t>Finding ID</t>
-  </si>
-  <si>
-    <t>Tool</t>
-  </si>
-  <si>
-    <t>Rule</t>
-  </si>
-  <si>
-    <t>File</t>
-  </si>
-  <si>
-    <t>Line</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Disposition</t>
-  </si>
-  <si>
-    <t>Reviewer</t>
-  </si>
-  <si>
-    <t>SA-001</t>
-  </si>
-  <si>
-    <t>IAR Static Analysis</t>
-  </si>
-  <si>
-    <t>MISRA-C:2012 Rule 14.4</t>
-  </si>
-  <si>
-    <t>xcr24.c</t>
-  </si>
-  <si>
-    <t>Controlling expression violation.</t>
-  </si>
-  <si>
-    <t>Warning</t>
-  </si>
-  <si>
-    <t>Modify condition</t>
-  </si>
-  <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>SA-002</t>
-  </si>
-  <si>
-    <t>cppcheck</t>
-  </si>
-  <si>
-    <t>MISRA-C:2012 Rule 10.8</t>
-  </si>
-  <si>
-    <t>trim.c</t>
-  </si>
-  <si>
-    <t>Cast expression issue.</t>
-  </si>
-  <si>
-    <t>Review cast</t>
-  </si>
-  <si>
-    <t>Deviation</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>XCR24</t>
-  </si>
-  <si>
-    <t>MCU</t>
-  </si>
-  <si>
-    <t>STM32F446RE</t>
-  </si>
-  <si>
-    <t>Compiler</t>
-  </si>
-  <si>
-    <t>IAR</t>
-  </si>
-  <si>
-    <t>Git Commit</t>
-  </si>
-  <si>
-    <t>Build Date</t>
-  </si>
-  <si>
-    <t>Release Date</t>
-  </si>
-  <si>
-    <t>Release Type</t>
-  </si>
-  <si>
-    <t>Initial Release</t>
-  </si>
-  <si>
-    <t>Added</t>
-  </si>
-  <si>
-    <t>Changed</t>
-  </si>
-  <si>
-    <t>Unit Test</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>Static Analysis / MISRA</t>
-  </si>
-  <si>
-    <t>Binary</t>
-  </si>
-  <si>
-    <t>XCR24_FW_V1.0.0.hex / .bin</t>
-  </si>
-  <si>
-    <t>Architecture ID</t>
-  </si>
-  <si>
-    <t>Source File / Function</t>
-  </si>
-  <si>
-    <t>Unit/Integration Test ID</t>
-  </si>
-  <si>
-    <t>System Test ID</t>
-  </si>
-  <si>
-    <t>Static Analysis</t>
-  </si>
-  <si>
-    <t>Release Version</t>
-  </si>
-  <si>
-    <t>Overall Status</t>
-  </si>
-  <si>
-    <t>XCR24 initialization</t>
-  </si>
-  <si>
-    <t>ARC-001, ARC-003</t>
-  </si>
-  <si>
-    <t>xcr24.c / xcr24_init()</t>
-  </si>
-  <si>
-    <t>XCR24 SPI register R/W</t>
-  </si>
-  <si>
-    <t>ARC-003, ARC-004</t>
-  </si>
-  <si>
-    <t>drv_xcr24.c / xcr24_write_reg()</t>
-  </si>
-  <si>
-    <t>12-bit DAC setting</t>
-  </si>
-  <si>
-    <t>drv_xcr24.c / xcr24_set_dac()</t>
-  </si>
-  <si>
-    <t>UT-001~004</t>
-  </si>
-  <si>
-    <t>drv_adc.c / adc_measure()</t>
-  </si>
-  <si>
-    <t>xcr24_trim.c / xcr24_trim()</t>
-  </si>
-  <si>
-    <t>Parse and dispatch commands.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UART Driver, XCR24 Driver</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FW-REQ-002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Draft</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FW-REQ-001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Peripheral</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inferface</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Trim</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UART command line interface</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>External DAC using I2C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>External ADC using SPI</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC24R Trim</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XD12R Trim</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XC24R Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>XD12R Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FW-REQ-006</t>
-  </si>
-  <si>
-    <t>FW-REQ-007</t>
-  </si>
-  <si>
-    <t>FW-REQ-008</t>
-  </si>
-  <si>
-    <t>FW-REQ-009</t>
-  </si>
-  <si>
-    <t>Timer Input Capture for frequency measure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SPI for control XC24R / External ADC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>I2C for External DAC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Timer for us delay</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Timer Interrupt for Vsync</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FW-REQ-010</t>
-  </si>
-  <si>
-    <t>FW-REQ-011</t>
-  </si>
-  <si>
-    <t>FW-REQ-012</t>
-  </si>
-  <si>
-    <t>FW-REQ-013</t>
-  </si>
-  <si>
-    <t>FW-REQ-014</t>
-  </si>
-  <si>
-    <t>FW-REQ-015</t>
-  </si>
-  <si>
-    <t>Control XC24R using SPI</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Control XD12R using Serial Interface or XC24R</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -821,7 +1030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -833,9 +1042,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1138,20 +1352,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:N17"/>
+  <dimension ref="B2:I18"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="4" max="4" width="86.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1177,15 +1393,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -1193,24 +1409,21 @@
       <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
@@ -1219,244 +1432,246 @@
         <v>14</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="I4" s="5"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="I5" s="5"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="4" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B9" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B10" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B11" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B12" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B13" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B14" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="4" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="4" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
         <v>12</v>
       </c>
@@ -1464,199 +1679,527 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B17" s="4" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="E17" s="5"/>
       <c r="F17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G17" s="5"/>
       <c r="H17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="4"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:I7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CC8A9ECE-FE41-4C2F-832C-97EAE43D07AA}">
+          <x14:formula1>
+            <xm:f>Common!$D$3:$D$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>H3:H18</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5DF9B7D1-31DB-4402-87DE-866074A4475D}">
+          <x14:formula1>
+            <xm:f>Common!$B$3:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A450BA07-13EB-4D36-880F-44F80B40A943}">
+          <x14:formula1>
+            <xm:f>Common!$C$3:$C$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>F3:F17</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:I7"/>
+  <dimension ref="B2:I22"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="4" max="4" width="22.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="92.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.08203125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="2:9" ht="34" x14ac:dyDescent="0.45">
+      <c r="B8" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B10" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B11" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B12" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="2"/>
+      <c r="D12" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B13" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B14" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B15" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B16" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B17" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:I7" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="B2:I7" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:I17">
+      <sortCondition descending="1" ref="C2:C7"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1F143727-0189-441B-AF85-05A98769C614}">
+          <x14:formula1>
+            <xm:f>Common!$D$3:$D$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>H3:H17</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1678,25 +2221,25 @@
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>27</v>
@@ -1707,25 +2250,25 @@
     </row>
     <row r="3" spans="2:10" ht="34" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>8</v>
@@ -1736,25 +2279,25 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -1765,25 +2308,25 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>16</v>
@@ -1794,25 +2337,25 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
@@ -1847,28 +2390,28 @@
   <sheetData>
     <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>27</v>
@@ -1879,22 +2422,22 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -1905,22 +2448,22 @@
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1931,22 +2474,22 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1957,22 +2500,22 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1986,24 +2529,24 @@
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -2030,34 +2573,34 @@
   <sheetData>
     <row r="2" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>7</v>
@@ -2071,18 +2614,18 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -2090,24 +2633,24 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -2121,18 +2664,18 @@
         <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -2146,18 +2689,18 @@
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2171,18 +2714,18 @@
         <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -2213,34 +2756,34 @@
   <sheetData>
     <row r="2" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>6</v>
@@ -2251,69 +2794,69 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F3" s="2">
         <v>123</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2">
         <v>245</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="M4" s="2"/>
     </row>
@@ -2336,94 +2879,94 @@
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B7" s="2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B14" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.45">
@@ -2431,7 +2974,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.45">
@@ -2439,23 +2982,23 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B17" s="2" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B18" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2490,28 +3033,28 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
@@ -2519,26 +3062,26 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K3" s="2"/>
     </row>
@@ -2547,26 +3090,26 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K4" s="2"/>
     </row>
@@ -2575,26 +3118,26 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K5" s="2"/>
     </row>
@@ -2603,16 +3146,16 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
@@ -2620,7 +3163,7 @@
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K6" s="2"/>
     </row>
@@ -2629,16 +3172,16 @@
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
@@ -2646,7 +3189,7 @@
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -2655,4 +3198,76 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4EECE6E-04CB-4201-95F0-D342C469E1BD}">
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/X-Series/XD12R/Jig/XD12R_GT1009A1R0_XC24R_GT1033A0R0/Docs/Firmware_Development_Documentation.xlsx
+++ b/X-Series/XD12R/Jig/XD12R_GT1009A1R0_XC24R_GT1033A0R0/Docs/Firmware_Development_Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD12R\Jig\XD12R_GT1009A1R0_XC24R_GT1033A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C24AE6-FCBD-41C7-9F70-4D636F61A879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D2E801-031F-442F-B2AB-8F7EB4F5D125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirement" sheetId="1" r:id="rId1"/>
@@ -1030,7 +1030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1048,6 +1048,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2249,118 +2252,118 @@
       </c>
     </row>
     <row r="3" spans="2:10" ht="34" x14ac:dyDescent="0.45">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="7" t="s">
         <v>12</v>
       </c>
     </row>
